--- a/artfynd/A 61157-2025 artfynd.xlsx
+++ b/artfynd/A 61157-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
